--- a/simulations/correction_peat_market/tech_ARC_peat_corr.xlsx
+++ b/simulations/correction_peat_market/tech_ARC_peat_corr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\simulations\correction_peat_market\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBA23723-6A55-4077-BB82-94D0B3B8D429}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0D44AB7-BE51-4160-B916-B0777F9937F7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930" activeTab="3" xr2:uid="{D746D7D5-B0A8-4858-AD5A-93AA09E65399}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930" activeTab="2" xr2:uid="{D746D7D5-B0A8-4858-AD5A-93AA09E65399}"/>
   </bookViews>
   <sheets>
     <sheet name="id_tech" sheetId="2" r:id="rId1"/>
